--- a/output/第10期計画_第9期施策別評価表と暫定評価ルール.xlsx
+++ b/output/第10期計画_第9期施策別評価表と暫定評価ルール.xlsx
@@ -3155,7 +3155,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>★達成率は受領年度のみで算定する。3年度分と誤読されないようにする</t>
+          <t>達成率は受領年度のみで算定する。3年度分と誤読されないようにする</t>
         </is>
       </c>
     </row>
@@ -3182,7 +3182,7 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>★「実施されなかった」ではない。把握できなかったことと実施されなかったことは別である</t>
+          <t>「実施されなかった」ではない。把握できなかったことと実施されなかったことは別である</t>
         </is>
       </c>
     </row>
@@ -3436,7 +3436,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>★目標は「令和5年度の実績を維持」であり、認定率の引下げを目標としたものではない。1.0ポイントの上昇は年齢構成の変化によるもので、同一年齢層でみると75歳以上は1.8ポイント低下している。「未達であるが実態が悪化したとは言えない」</t>
+          <t>目標は「令和5年度の実績を維持」であり、認定率の引下げを目標としたものではない。1.0ポイントの上昇は年齢構成の変化によるもので、同一年齢層でみると75歳以上は1.8ポイント低下している。「未達であるが実態が悪化したとは言えない」</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_第9期施策別評価表と暫定評価ルール.xlsx
+++ b/output/第10期計画_第9期施策別評価表と暫定評価ルール.xlsx
@@ -3631,7 +3631,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>成果（アウトカム）は全国平均の123.5％と高い一方、活動（アウトプット）は全国の23.2〜55.6％にとどまる。活動を国の様式で記録・報告する仕組みがなかったことによる</t>
+          <t>成果（アウトカム）は全国平均の123.5％と高い一方、活動（アウトプット）は全国の23.2〜55.6％にとどまる。原因は未実施・要件未充足・記録又は報告の不備のいずれかであるが未確認</t>
         </is>
       </c>
     </row>
@@ -3707,7 +3707,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>介護サービス自給率（6区分平均）</t>
+          <t>介護サービス自給率（算定可能区分の単純平均（美瑛6区分、東川・東神楽5区分））</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>交付金評価で成果は全国平均の123.5％である一方、活動は全国の23.2〜55.6％にとどまる。活動を国の様式で記録・報告する仕組みがなかったことによる。第10期はロジックモデルに沿った記載に改める。</t>
+          <t>交付金評価で成果は全国平均の123.5％である一方、活動は全国の23.2〜55.6％にとどまる。原因は、未実施・要件未充足・記録又は報告の不備のいずれかであるが未確認である。第10期はロジックモデルに沿った記載に改める。</t>
         </is>
       </c>
       <c r="D29" s="12" t="n"/>

--- a/output/第10期計画_第9期施策別評価表と暫定評価ルール.xlsx
+++ b/output/第10期計画_第9期施策別評価表と暫定評価ルール.xlsx
@@ -3348,7 +3348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>8.0％（目標）</t>
+          <t>7.3％（R4）</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -3525,14 +3525,14 @@
           <t>8.8％（R7）</t>
         </is>
       </c>
-      <c r="E9" s="10" t="inlineStr">
-        <is>
-          <t>達成</t>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>未達</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>ただし目標の根拠とした国の統計と実績の統計が異なる。総合事業ベースでは全国平均の31％にとどまる</t>
+          <t>第9期の年度目標はR6 8.0％・R7 9.0％・R8 10.0％であり、R7目標9.0％に0.2ポイント届かない。基準値からの＋1.5ポイントは統計的に有意である。なお目標の根拠とした国の統計と実績の統計が異なる。国と同じ総合事業ベースでは令和6年度3.53％で、令和2年度1.6％から2.2倍に回復したが国の水準8％を大きく下回る</t>
         </is>
       </c>
     </row>
@@ -3731,18 +3731,342 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="39" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>注1）本シートの評価は事業実績を要さない。資料提供依頼No.13が受領できない場合でも、第9期の成果評価はここまで行える。注2）【1】①の評価（未達であるが実態が悪化したとは言えない）は、計画本文に書いてよいかの確認を要する（別管理表 確認事項A No.11）。注3）【2】②の交付金評価は令和5年調査（令和6年度分の指標）である。令和6年・令和7年調査の得点があれば経年比較ができる（資料提供依頼No.5）。</t>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>【3　計画値と実績値の対比（見える化システムの総括表）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" s="4" t="inlineStr"/>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>指標</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>R6対計画比</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>R7対計画比</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>判定</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>評価の内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="44" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>①</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>第1号被保険者数</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>99.3％</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>98.5％</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>計画内</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>実績9,143人・9,119人。計画をやや下回って推移している</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="44" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>②</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>要介護認定者数</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>97.7％</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>96.0％</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>計画内</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>実績1,942人・1,943人。認定者数の伸びは計画より緩やか</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="44" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>③</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>要介護認定率</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>98.4％</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>97.4％</t>
+        </is>
+      </c>
+      <c r="E23" s="10" t="inlineStr">
+        <is>
+          <t>計画内</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>実績21.24％・21.31％（各年9月月報）</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="44" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>④</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>総給付費</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>96.3％</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>97.8％</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>計画内</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>実績2,817百万円・2,915百万円。代表KPI H15（給付費の計画乖離率）はR6▲3.66％・R7▲2.17％で目標±5％以内を満たす</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="44" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>⑤</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　施設サービス給付費</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>104.3％</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>100.8％</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>計画超過</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>唯一計画を上回る区分。介護老人保健施設がR6 107.3％</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="44" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>⑥</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　居住系サービス給付費</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>83.8％</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>88.3％</t>
+        </is>
+      </c>
+      <c r="E26" s="11" t="inlineStr">
+        <is>
+          <t>計画未達</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>乖離が最も大きい。特定施設入居者生活介護79.0％・84.8％、認知症対応型共同生活介護86.2％・90.1％</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="44" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>⑦</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　在宅サービス給付費</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>93.7％</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>98.4％</t>
+        </is>
+      </c>
+      <c r="E27" s="10" t="inlineStr">
+        <is>
+          <t>計画内</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>R7に回復。地域密着型通所介護66.6％と居宅療養管理指導154.9％が相殺している</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="44" customHeight="1">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>⑧</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>第1号1人当たり給付費</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>97.0％</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>99.3％</t>
+        </is>
+      </c>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>計画内</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>実績308,126円・319,696円</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="44" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>⑨</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>保険料基準額（期単位）</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>94％</t>
+        </is>
+      </c>
+      <c r="E29" s="11" t="inlineStr">
+        <is>
+          <t>計画未達</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>第9期の計画6,428円（準備基金取崩後）に対し実績6,069円。令和8年度の実績が未登録の状態の値である</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="52" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>注1）本シートの評価は事業実績を要さない。資料提供依頼No.13が受領できない場合でも、第9期の成果評価はここまで行える。注2）【1】①の評価（未達であるが実態が悪化したとは言えない）は、計画本文に書いてよいかの確認を要する（別管理表 確認事項A No.11）。注3）【2】②の交付金評価は令和5年調査（令和6年度分の指標）である。令和6年・令和7年調査の得点があれば経年比較ができる（資料提供依頼No.5）。注4）【3】は令和8年8月31日受領の見える化システムの総括表による。総括表の「第9期累計」欄は3か年の計画値に2か年の実績値を対比したものであり達成率ではないため、年度別の対計画比を用いた。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A19:F19"/>
+  <mergeCells count="5">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A31:F31"/>
     <mergeCell ref="A4:F4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4209,12 +4533,12 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>第9期は必要保険料月額ベースで算定可</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>算定可</t>
+          <t>R6 ▲3.66％／R7 ▲2.17％（総給付費ベース）</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>達成</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">

--- a/output/第10期計画_第9期施策別評価表と暫定評価ルール.xlsx
+++ b/output/第10期計画_第9期施策別評価表と暫定評価ルール.xlsx
@@ -13,6 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_暫定評価ルール" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_成果評価" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_委員会用スコアカード" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_暫定評価" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -155,7 +156,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -188,6 +189,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -4906,4 +4913,1136 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>19施策の暫定評価（実績の受領前に判定できる範囲）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="52" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>資料提供依頼No.13（令和6〜8年度の施策・事業実績）の受領前に、保険者機能強化推進交付金等の大項目別得点（53項目・構成3町・3か年）を19施策に割り当て、判定できる範囲を示す。得点率は3町計の得点を3町計の配点で除したもの。交付金は取組の有無と要件の充足を測るものであり、事業量・対象実人数・決算額を測るものではない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>【1　施策別の暫定評価】</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>施策</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>交付金
+項目数</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>R6得点率</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>R7得点率</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>R8得点率</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>暫定判定</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>判定の根拠（交付金）</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>他の資料による補足</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="40" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>圏域ビジョン・戦略の推進</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>44％</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>44％</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>44％</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>取組あり・横ばい</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>5項目のうち3か年とも0点は2項目（評価結果の活用、今年度の評価点）</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="40" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>在宅療養者支援に向けた医療機関との連携体制の構築</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>24％</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>28％</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>30％</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>取組あり・改善</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>5項目のうち3か年とも0点は0項目</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>見える化の対計画比により居宅療養管理指導が令和7年度154.9％、訪問看護が95.6％。在宅医療の利用は伸びている</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="40" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>高齢者の状況に応じたサービスの提供</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>35％</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>30％</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>30％</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>取組あり・横ばい</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>2項目のうち3か年とも0点は0項目</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>見える化の対計画比により総給付費97.8％（令和7年度）。地域密着型通所介護66.6％・短期入所生活介護65.0％が下振れ</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="40" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>1-4</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>高齢者の虐待防止の推進</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>交付金では判定できない</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>該当する交付金の評価項目がない</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>地域共生社会を目指したまちづくりの推進</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>41％</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>49％</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>50％</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>取組あり・改善</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>4項目のうち3か年とも0点は0項目</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>介護予防・日常生活支援総合事業の推進</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>34％</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>33％</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>26％</t>
+        </is>
+      </c>
+      <c r="G11" s="11" t="inlineStr">
+        <is>
+          <t>取組あり・低下</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>5項目のうち3か年とも0点は0項目</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>総合事業調査により令和6年度の通いの場は25箇所・330人（参加率3.53％）。令和2年度の3箇所・151人から回復した</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>認知症施策推進大綱を踏まえた施策の推進</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>36％</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>30％</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>30％</t>
+        </is>
+      </c>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
+          <t>取組あり・低下</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>6項目のうち3か年とも0点は1項目（認知症サポーターステップアップ講座修了者数）</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>2-4</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>高齢者の住まいと生活支援の一体化支援に向けた検討</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>交付金では判定できない</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>該当する交付金の評価項目がない</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="40" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>2-5</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>地域ケア会議の推進</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>58％</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>75％</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>88％</t>
+        </is>
+      </c>
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>取組あり・改善</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>2項目のうち3か年とも0点は0項目</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="40" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>2-6</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>包括的な支援体制の整備</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>29％</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>31％</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>23％</t>
+        </is>
+      </c>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
+          <t>取組あり・低下</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>2項目のうち3か年とも0点は0項目</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>総合事業調査により一般介護予防事業評価事業及び総合事業の事業評価は3町とも実施していない</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="40" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>高齢者による主体的な健康づくり・介護予防の推進</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>56％</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>55％</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>50％</t>
+        </is>
+      </c>
+      <c r="G16" s="11" t="inlineStr">
+        <is>
+          <t>取組あり・低下</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>4項目のうち3か年とも0点は0項目</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>総合事業調査により週1回以上の通いの場は東神楽町のみ11箇所。東川町・美瑛町にはない</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="40" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>地域リハビリテーション支援体制の構築</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>48％</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>48％</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>48％</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>取組あり・横ばい</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>1項目のうち3か年とも0点は0項目</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>総合事業調査により地域リハビリテーション活動支援事業は美瑛町のみ実施。理学療法士等の派遣は通いの場へ24回</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="40" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>3-3</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>高齢者の保健事業・介護予防の一体化の推進</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>67％</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>67％</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>67％</t>
+        </is>
+      </c>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>取組あり・横ばい</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>2項目のうち3か年とも0点は0項目</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>総合事業調査により国保データベース（KDB）の活用は美瑛町・東神楽町の2町。東川町は活用していない</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="40" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>3-4</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>地域支援事業の連動性の確保</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>29％</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>27％</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>29％</t>
+        </is>
+      </c>
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>取組あり・横ばい</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>2項目のうち3か年とも0点は0項目</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="40" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>4-1</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>介護サービスの生産性向上</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>62％</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>61％</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>61％</t>
+        </is>
+      </c>
+      <c r="G20" s="8" t="inlineStr">
+        <is>
+          <t>取組あり・横ばい</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>2項目のうち3か年とも0点は0項目</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="40" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>4-2</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>介護サービス事業者の適正・円滑な運営</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>交付金では判定できない</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>該当する交付金の評価項目がない</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="40" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>4-3</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>介護給付費の適正化</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>23％</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>38％</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>38％</t>
+        </is>
+      </c>
+      <c r="G22" s="10" t="inlineStr">
+        <is>
+          <t>取組あり・改善</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>4項目のうち3か年とも0点は1項目（ケアプラン点検の実施状況）</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>見える化の対計画比により総給付費の計画乖離率は令和6年度▲3.66％・令和7年度▲2.17％で目標±5％以内</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="40" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>4-4</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>人材確保・育成の推進</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>26％</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>24％</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>23％</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>取組あり・横ばい</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>4項目のうち3か年とも0点は2項目（介護の仕事の魅力に関する研修の実施状況、介護人材の定着・資質向上に関する研修の実施状況）</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>見える化M2系列により職種別従事者数を把握している</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="40" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>5-1</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>災害や感染症対策に係る体制整備</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>交付金では判定できない</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>該当する交付金の評価項目がない</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>【2　暫定判定の内訳】</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="32" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>施策数</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>該当する施策</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr"/>
+      <c r="E27" s="4" t="inlineStr"/>
+      <c r="F27" s="4" t="inlineStr"/>
+      <c r="G27" s="4" t="inlineStr"/>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>実績の受領後にできること</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr"/>
+    </row>
+    <row r="28" ht="34" customHeight="1">
+      <c r="A28" s="14" t="inlineStr">
+        <is>
+          <t>取組あり・改善</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>1-2、2-1、2-5、4-3</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr"/>
+      <c r="E28" s="5" t="inlineStr"/>
+      <c r="F28" s="5" t="inlineStr"/>
+      <c r="G28" s="5" t="inlineStr"/>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>令和6年度から令和8年度にかけて得点率が5ポイント以上上がった施策。事業量・対象実人数を加えて達成度を判定する</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29" ht="34" customHeight="1">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>取組あり・横ばい</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>1-1、1-3、3-2、3-3、3-4、4-1、4-4</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr"/>
+      <c r="E29" s="5" t="inlineStr"/>
+      <c r="F29" s="5" t="inlineStr"/>
+      <c r="G29" s="5" t="inlineStr"/>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>得点率の変化が±5ポイント以内の施策。取組は継続しているが要件の充足が進んでいない</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30" ht="34" customHeight="1">
+      <c r="A30" s="15" t="inlineStr">
+        <is>
+          <t>取組あり・低下</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>2-2、2-3、2-6、3-1</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr"/>
+      <c r="E30" s="5" t="inlineStr"/>
+      <c r="F30" s="5" t="inlineStr"/>
+      <c r="G30" s="5" t="inlineStr"/>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>得点率が5ポイント以上下がった施策。低下の理由（要件の変更か取組の縮小か）を確認する</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31" ht="34" customHeight="1">
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t>取組を確認できない</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr"/>
+      <c r="E31" s="5" t="inlineStr"/>
+      <c r="F31" s="5" t="inlineStr"/>
+      <c r="G31" s="5" t="inlineStr"/>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>3か年とも該当項目がすべて0点の施策。取組の不在か要件未充足か報告の不備かは評価調書（資料No.5）による</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr"/>
+    </row>
+    <row r="32" ht="34" customHeight="1">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>交付金では判定できない</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>1-4、2-4、4-2、5-1</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr"/>
+      <c r="E32" s="5" t="inlineStr"/>
+      <c r="F32" s="5" t="inlineStr"/>
+      <c r="G32" s="5" t="inlineStr"/>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>該当する評価項目がない施策。実績（資料No.13）がなければ判定できない</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr"/>
+    </row>
+    <row r="34" ht="110" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>注1）本シートは暫定の判定である。交付金の評価項目は取組の有無と要件の充足を測るものであり、事業量・対象実人数・決算額を測るものではない。プロセス評価の代替にはならない。
+注2）1施策に複数の交付金項目が対応し、1つの交付金項目が複数の施策に対応する場合がある（例：介護人材の確保・定着の取組状況は4-1と4-4の双方に対応する）。割当ては受託者によるものであり、発注者のご確認を要する。
+注3）0点の理由（取組の不在・要件未充足・報告の不備）は交付金の得点からは判別できない。評価調書（資料提供依頼No.5）による。
+注4）交付金の評価は構成市町村ごとに行われる。本シートの得点率は3町計の得点を3町計の配点で除したものであり、町別の状況は「令和8年8月28日受領資料の点検結果」による。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A34:I34"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A26:I26"/>
+    <mergeCell ref="A2:I2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>